--- a/PyCharmMiscProject/zayavki.xlsx
+++ b/PyCharmMiscProject/zayavki.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:56:30</t>
+          <t>15:06:16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,14 +485,88 @@
           <t>santeh</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>kzkzkzkz</t>
-        </is>
+      <c r="G2" t="n">
+        <v>22</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Выполнена</t>
+          <t>Новая</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15:06:23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Савченко Валерия Андреевна</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cleaning</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>223</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15:06:29</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Савченко Валерия Андреевна</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>22353556</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Новая</t>
         </is>
       </c>
     </row>
